--- a/artfynd/A 36046-2024 artfynd.xlsx
+++ b/artfynd/A 36046-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>69889283</v>
       </c>
       <c r="B2" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452934.8312568657</v>
+        <v>452935</v>
       </c>
       <c r="R2" t="n">
-        <v>6301220.182621296</v>
+        <v>6301220</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +757,9 @@
           <t>2018-03-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -829,12 +814,7 @@
         <v>69889309</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452934.8312568657</v>
+        <v>452935</v>
       </c>
       <c r="R3" t="n">
-        <v>6301220.182621296</v>
+        <v>6301220</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,19 +889,9 @@
           <t>2018-03-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-03-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -967,12 +937,7 @@
         <v>95950723</v>
       </c>
       <c r="B4" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452922.8947525726</v>
+        <v>452923</v>
       </c>
       <c r="R4" t="n">
-        <v>6301182.040093803</v>
+        <v>6301182</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1048,19 +1013,9 @@
           <t>2021-09-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1090,6 +1045,244 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>69889879</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sälleberg, Sälleberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>452975</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6301356</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-03-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-03-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69889886</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sälleberg, Sälleberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>452961</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6301378</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-03-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-03-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36046-2024 artfynd.xlsx
+++ b/artfynd/A 36046-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69889283</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -931,6 +941,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69889309</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95950723</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69889879</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1283,8 +1308,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69889886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>